--- a/life_table4.xlsx
+++ b/life_table4.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\NRES-470\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8159C853-93AC-43D8-B918-548012AA1A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="16875" windowHeight="8940"/>
+    <workbookView xWindow="28680" yWindow="-1620" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="life_table4" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -572,9 +578,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -612,7 +618,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -718,7 +724,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -860,7 +866,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -870,6 +876,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -898,7 +909,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>350</v>
+        <v>212</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -909,10 +920,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C4">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -920,7 +931,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C5">
         <v>4.2</v>
@@ -931,10 +942,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
